--- a/data_extactor/batch_10_fa/trimmed/batch_0059_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0059_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زیست‌شناسی | تولید و فرآوری | ایمنی و امنیت عمومی | حقوق و مقررات دولتی | شیمی</t>
+          <t>خدمات مشتری و شخصی | زیست‌شناسی | تولید و فرآوری | ایمنی و امنیت عمومی | قانون و دولت | شیمی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت کنترل | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | هماهنگی اندام‌ها | چابکی دستی</t>
+          <t>بینایی نزدیک | دقت کنترل | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | هماهنگی چند عضو | مهارت دستی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | تکنسین‌های کشاورزی | کارگران مزارع، باغات و گلخانه‌ها | کارگران باغبانی و محوطه‌سازی | کارگران کنترل آفات و سم‌پاشی | دانشمندان علوم خاک و گیاه‌شناسی | هرس‌کنندگان درختان</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | کارگران زراعت، نهالستان و گلخانه | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران سم‌پاشی و دفع آفات | متخصصان خاک‌شناسی و علوم گیاهی | هرس‌کنندگان و پیرایندگان درختان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Outlook | Microsoft Word | Facebook</t>
+          <t>Facebook | Microsoft Outlook | Microsoft Word</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک</t>
+          <t>خدمات مشتری و شخصی | مکانیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | چابکی دستی | هماهنگی اندام‌ها | حساسیت به مسئله | قدرت ایستا | ثبات دست و بازو | تعادل کلی بدن</t>
+          <t>دقت کنترل | مهارت دستی | هماهنگی چند عضو | حساسیت به مسئله | قدرت ایستا | ثبات دست و بازو | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>چوب‌بُران و درخت‌اندازان | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | کارگران جنگل‌داری و حفاظت | کارگران باغبانی و محوطه‌سازی | اپراتورهای ماشین‌آلات چوب‌بُری و الوارسازی | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | تنظیم‌کنندگان و اپراتورهای اره‌کشی چوب</t>
+          <t>درخت‌اندازان و چوب‌بُران جنگل | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارگران باغبانی، فضای سبز و نگهداری محوطه | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | مکانیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | شیمی | زیست‌شناسی</t>
+          <t>تولید مواد غذایی | مکانیک | زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | شیمی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستا | استحکام تنه | استقامت بدنی</t>
+          <t>مهارت دستی | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران باغبانی و محوطه‌سازی | هرس‌کنندگان و پیرایندگان درختان | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | سرپرستان رده‌اول کارگران باغبانی، فضای سبز و محوطه‌سازی | کارگران کنترل آفات و سم‌پاشی | کارگران مزارع، باغات و گلخانه‌ها | کارگران تعمیرات و نگهداری عمومی</t>
+          <t>کارگران باغبانی، فضای سبز و نگهداری محوطه | هرس‌کنندگان و پیرایندگان درختان | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران سم‌پاشی و دفع آفات | کارگران زراعت، نهالستان و گلخانه | کارگران عمومی تعمیرات و نگهداری تاسیسات</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | مدیریت و امور اداری | اقتصاد و حسابداری | ایمنی و امنیت عمومی | پرسنلی و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | اقتصاد و حسابداری | ایمنی و امنیت عمومی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی‌ها | صندوق‌داران | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | سرپرستان رده‌اول کارکنان فروش خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران مراکز بازی و تفریحات | متصدیان باجه‌های بانکی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | صندوق‌داران | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | پرسنلی و منابع انسانی | آموزش و تدریس | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | آموزش و پرورش | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | سرپرستان رده‌اول مهمانداران و متصدیان خدمات مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده‌اول کارکنان فروش خرده‌فروشی | مدیران عمومی و عملیاتی | مربیان و کارشناسان امور تفریحی و اوقات فراغت</t>
+          <t>سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | مدیران کل و مدیران عملیات | کارکنان و متصدیان امور تفریحی و اوقات فراغت</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ایمنی و امنیت عمومی | روان‌شناسی | پرسنلی و منابع انسانی | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | ایمنی و امنیت عمومی | روان‌شناسی | پرسنل و منابع انسانی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | وضوح گفتار | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارکنان خدمات نظافتی و خانه‌داری | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | کارشناسان منابع انسانی | مدیران خدمات بهداشتی و درمانی | مشاوران و سرپرستان خوابگاه‌ها و اقامتگاه‌ها</t>
+          <t>مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان منابع انسانی | مدیران خدمات درمانی و بهداشتی | سرپرستان و مشاوران خوابگاه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>استراتژی‌های یادگیری | سخن گفتن | تفکر انتقادی | یادگیری فعال | شنیدن فعال | نظارت</t>
+          <t>راهبردهای یادگیری | سخن گفتن | تفکر انتقادی | یادگیری فعال | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | روان‌شناسی | مدیریت و امور اداری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | وضوح گفتار | استقامت بدنی | هماهنگی اندام‌ها | چابکی دستی</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | وضوح گفتار | استقامت | هماهنگی چند عضو | مهارت دستی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پرورش‌دهندگان حیوانات | مراقبان و نگهداران حیوانات | ماموران کنترل و زنده‌گیری حیوانات | دانشمندان علوم دامی | کارگران مزارع پرورش دام، طیور و آبزیان | دامپزشکان | تکنسین‌ها و کاردان‌های دامپزشکی</t>
+          <t>تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | مراقبان و نگهداران حیوانات | ماموران کنترل و ساماندهی حیوانات | متخصصان علوم دامی | کارگران پرورش دام، طیور و آبزیان | دامپزشکان | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور دفتری و اداری | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | دید نزدیک | قدرت ایستا | مرتب‌سازی اطلاعات | استحکام تنه</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | بینایی نزدیک | قدرت ایستا | ترتیب‌دهی اطلاعات | قدرت تنه</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرورش‌دهندگان حیوانات | ماموران کنترل و زنده‌گیری حیوانات | مربیان و رام‌کنندگان حیوانات | مدیران مزارع، دامپروری‌ها و سایر واحدهای کشاورزی | کارگران مزارع پرورش دام، طیور و آبزیان | دستیاران دامپزشک و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و کاردان‌های دامپزشکی</t>
+          <t>تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | ماموران کنترل و ساماندهی حیوانات | مربیان و رام‌کنندگان حیوانات | مدیران امور کشاورزی، دامپروری و شیلات | کارگران پرورش دام، طیور و آبزیان | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | چابکی انگشتان | مرتب‌سازی اطلاعات | چابکی دستی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | مهارت انگشتان | ترتیب‌دهی اطلاعات | مهارت دستی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی‌ها | صندوق‌داران | کارمندان پذیرش و اجاره کالا | کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | مدیران مراکز بازی و تفریحات | فروشندگان خرده‌فروشی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | فروشندگان خرده‌فروشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | وضوح گفتار | مرتب‌سازی اطلاعات | استدلال ریاضی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی‌ها | کارمندان حسابداری، دفاتر مالی و حسابرسی | صندوق‌داران | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | مدیران مراکز بازی و تفریحات | فروشندگان خرده‌فروشی | متصدیان باجه‌های بانکی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | کارمندان دفترداری، حسابداری و امور حسابرسی | صندوق‌داران | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | فروشندگان خرده‌فروشی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
